--- a/clientportal/Raw Data - 5823_OC-CR.xlsx
+++ b/clientportal/Raw Data - 5823_OC-CR.xlsx
@@ -1226,15 +1226,15 @@
     <t>Contratación para dar continuidad al contrato CR-L1151-P00038</t>
   </si>
   <si>
+    <t>Proceso en Curso</t>
+  </si>
+  <si>
     <t>CR-L1151-P00070</t>
   </si>
   <si>
     <t>Contratación de consultor individual Ingeniero Especialista en Estructuras que apoye en la revisión de los diseños ejecutivos e inspección de campo para los proyectos de la nueva carretera a San Carlos RN No. 35 </t>
   </si>
   <si>
-    <t>Modificado En Revisión</t>
-  </si>
-  <si>
     <t>1.1.3.1</t>
   </si>
   <si>
@@ -1274,9 +1274,6 @@
     <t>Contratación de Consultor Individual Analista Financiero Contable  para asesoramiento en la gestión financiera  del Programa de Infraestructura Vial y Movilidad Urbana: Conectividad Resiliente</t>
   </si>
   <si>
-    <t>En Revisión</t>
-  </si>
-  <si>
     <t>1.1.3.2</t>
   </si>
   <si>
@@ -1487,6 +1484,9 @@
     <t>Rosy Isel Alvarado Mora</t>
   </si>
   <si>
+    <t>Heynner Céspedes Muñoz</t>
+  </si>
+  <si>
     <t>CR-L1151-P00001-C01</t>
   </si>
   <si>
@@ -1766,6 +1766,9 @@
     <t>P00051-C01-A1</t>
   </si>
   <si>
+    <t>P00054-C01-A1</t>
+  </si>
+  <si>
     <t>CR-L1151-P00001-C01-1</t>
   </si>
   <si>
@@ -1799,6 +1802,9 @@
     <t>CR-L1151-P00051-C01-1</t>
   </si>
   <si>
+    <t>CR-L1151-P00054-C01-1</t>
+  </si>
+  <si>
     <t>Línea No. 1</t>
   </si>
   <si>
@@ -1850,18 +1856,18 @@
     <t>Enterados.Por favor esperar a la revisión del Plan de Adquisiciones en revision por el BID, antes de tomar accion con relacion a este proceso.</t>
   </si>
   <si>
+    <t>En consideración con ajustes identificados por el UEP, se modifican las fechas de los hitos del proceso.</t>
+  </si>
+  <si>
+    <t>carlos.leiva@mopt.go.cr</t>
+  </si>
+  <si>
+    <t>Se realiza un ajuste en las fechas estimadas de los hitos</t>
+  </si>
+  <si>
     <t>Se ajustó el monto previsto para la contratación, pasando de US $1.000.000,00 a US $450.000,00.</t>
   </si>
   <si>
-    <t>carlos.leiva@mopt.go.cr</t>
-  </si>
-  <si>
-    <t>Se realiza un ajuste en las fechas estimadas de los hitos</t>
-  </si>
-  <si>
-    <t>En consideración con ajustes identificados por el UEP, se modifican las fechas de los hitos del proceso.</t>
-  </si>
-  <si>
     <t>CR-L1151-P00004</t>
   </si>
   <si>
@@ -1925,15 +1931,15 @@
     <t>Contratación de consultor individual que apoye a la Dirección del Departamento de Adquisiciones de Bienes Inmuebles del MOPT en la gestión de expropiaciones dela nueva carretera a San Carlos </t>
   </si>
   <si>
+    <t>La Gerencia del Programa no continuará con el proceso de Selección Directa CR-L1151-P00026, por lo anterior se procede a cancelarlo. </t>
+  </si>
+  <si>
+    <t>Este proceso de Selección Directa se cancela, debido a que la UEP estará promoviendo un nuevo proceso (3CV) para disponer de los servicios de la consultoría requerida.</t>
+  </si>
+  <si>
     <t>Se actualizará la forma de pago, para que la misma corresponda a día trabajado. </t>
   </si>
   <si>
-    <t>La Gerencia del Programa no continuará con el proceso de Selección Directa CR-L1151-P00026, por lo anterior se procede a cancelarlo. </t>
-  </si>
-  <si>
-    <t>Este proceso de Selección Directa se cancela, debido a que la UEP estará promoviendo un nuevo proceso (3CV) para disponer de los servicios de la consultoría requerida.</t>
-  </si>
-  <si>
     <t>Se ajustó el monto del proceso, considerando la previsión de la consultoría para todo el Programa (estimando 54 meses), tomando una tarifa fija mensual de US $6.000,00.</t>
   </si>
   <si>
@@ -1961,12 +1967,12 @@
     <t>Se cancela el proceso para atender observaciones del equipo del Banco, notificadas en fecha 09 de abril del 2025.</t>
   </si>
   <si>
+    <t>Contratación de consultor (según demanda) se considera un máximo de 22 días/mes con una tarifa diaria de US $250.00, para un total de US $66,000.00 (durante 1 año de servicios).</t>
+  </si>
+  <si>
     <t>Se ajusta el monto del proceso considerando la negociación entre las Partes, tarifa diaria de US$350.00 con un máximo de 22 días por mes, por un año de servicios (US$92,400.00)</t>
   </si>
   <si>
-    <t>Contratación de consultor (según demanda) se considera un máximo de 22 días/mes con una tarifa diaria de US $250.00, para un total de US $66,000.00 (durante 1 año de servicios).</t>
-  </si>
-  <si>
     <t>El monto de la contratación será de US $44,000.00, considerando una tarifa mensual de US $3,700.00.</t>
   </si>
   <si>
@@ -2042,12 +2048,12 @@
     <t>Contratación de servicios para la producción de elementos e insumos de publicidad para las comunicaciones del Programa de Infraestructura Vial y Movilidad Urbana: Conectividad Resiliente</t>
   </si>
   <si>
+    <t>El proceso se cancela considerando que el Consultor no reguló su condición ante el Ministerio de Hacienda y CCSS, por lo cual no se puede suscribir el contrato.</t>
+  </si>
+  <si>
     <t>Para la contratación del consultor se considera una tarifa mensual de USD$5000.00  por un plazo de hasta 12 meses.</t>
   </si>
   <si>
-    <t>El proceso se cancela considerando que el Consultor no reguló su condición ante el Ministerio de Hacienda y CCSS, por lo cual no se puede suscribir el contrato.</t>
-  </si>
-  <si>
     <t>Se considera un monto de contratación de US$200,000.00 correspondiente a 40 meses (finalización del programa) con una tarifa mensual de US$5,000.00</t>
   </si>
   <si>
@@ -2078,10 +2084,10 @@
     <t>Incorporación de nuevo proceso (SD) para dar continuidad al contrato CR-L1151-P00017.</t>
   </si>
   <si>
+    <t>Incorporación de nuevo proceso (SD) para dar continuidad al contrato CR-L1151-P00018.</t>
+  </si>
+  <si>
     <t>Para la SD CR-L1151-P00061 se han incorporado actividades adicionales por realizar en la prestación del servicio, por lo cual se ajustó la tarifa mensual a USD $6 000,00 </t>
-  </si>
-  <si>
-    <t>Incorporación de nuevo proceso (SD) para dar continuidad al contrato CR-L1151-P00018.</t>
   </si>
   <si>
     <t>Incorporación de nuevo proceso (SD) para dar continuidad al contrato CR-L1151-P00020.</t>
@@ -5987,7 +5993,7 @@
         <v>282</v>
       </c>
       <c r="S57" t="s">
-        <v>245</v>
+        <v>393</v>
       </c>
       <c r="T57"/>
       <c r="U57"/>
@@ -6002,7 +6008,7 @@
         <v>230</v>
       </c>
       <c r="B58" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C58" t="s">
         <v>232</v>
@@ -6011,7 +6017,7 @@
         <v>344</v>
       </c>
       <c r="E58" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F58"/>
       <c r="G58"/>
@@ -6047,7 +6053,7 @@
         <v>276</v>
       </c>
       <c r="S58" t="s">
-        <v>395</v>
+        <v>245</v>
       </c>
       <c r="T58"/>
       <c r="U58"/>
@@ -6064,7 +6070,7 @@
         <v>230</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s">
         <v>232</v>
@@ -6073,7 +6079,7 @@
         <v>344</v>
       </c>
       <c r="E59" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F59"/>
       <c r="G59"/>
@@ -6109,7 +6115,7 @@
         <v>251</v>
       </c>
       <c r="S59" t="s">
-        <v>395</v>
+        <v>245</v>
       </c>
       <c r="T59"/>
       <c r="U59"/>
@@ -6413,7 +6419,7 @@
         <v>276</v>
       </c>
       <c r="S64" t="s">
-        <v>409</v>
+        <v>245</v>
       </c>
       <c r="T64"/>
       <c r="U64"/>
@@ -6422,7 +6428,7 @@
       <c r="X64"/>
       <c r="Y64"/>
       <c r="Z64" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.3">
@@ -6475,7 +6481,7 @@
         <v>251</v>
       </c>
       <c r="S65" t="s">
-        <v>409</v>
+        <v>245</v>
       </c>
       <c r="T65"/>
       <c r="U65"/>
@@ -6484,7 +6490,7 @@
       <c r="X65"/>
       <c r="Y65"/>
       <c r="Z65" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -6527,13 +6533,13 @@
         <v>243</v>
       </c>
       <c r="C2" t="n" s="5">
-        <v>45737</v>
+        <v>46031</v>
       </c>
       <c r="D2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6547,10 +6553,10 @@
         <v>45775</v>
       </c>
       <c r="D3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6561,30 +6567,30 @@
         <v>243</v>
       </c>
       <c r="C4" t="n" s="5">
-        <v>46031</v>
+        <v>45737</v>
       </c>
       <c r="D4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E4" t="s">
         <v>604</v>
-      </c>
-      <c r="E4" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B5" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>46239</v>
       </c>
       <c r="D5" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E5" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6598,10 +6604,10 @@
         <v>46250</v>
       </c>
       <c r="D6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E6" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6615,10 +6621,10 @@
         <v>46250</v>
       </c>
       <c r="D7" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E7" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6632,61 +6638,61 @@
         <v>45401</v>
       </c>
       <c r="D8" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E8" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B9" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>45749</v>
       </c>
       <c r="D9" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E9" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" t="s">
         <v>613</v>
-      </c>
-      <c r="B10" t="s">
-        <v>611</v>
       </c>
       <c r="C10" t="n" s="5">
         <v>45749</v>
       </c>
       <c r="D10" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E10" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B11" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>45749</v>
       </c>
       <c r="D11" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E11" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -6700,10 +6706,10 @@
         <v>45737</v>
       </c>
       <c r="D12" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -6717,10 +6723,10 @@
         <v>45785</v>
       </c>
       <c r="D13" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E13" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -6734,10 +6740,10 @@
         <v>45737</v>
       </c>
       <c r="D14" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E14" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -6751,10 +6757,10 @@
         <v>45834</v>
       </c>
       <c r="D15" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E15" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -6768,10 +6774,10 @@
         <v>45785</v>
       </c>
       <c r="D16" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E16" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -6785,10 +6791,10 @@
         <v>45785</v>
       </c>
       <c r="D17" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -6802,78 +6808,78 @@
         <v>45737</v>
       </c>
       <c r="D18" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E18" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B19" t="s">
         <v>443</v>
-      </c>
-      <c r="B19" t="s">
-        <v>444</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>45737</v>
       </c>
       <c r="D19" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E19" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>442</v>
+      </c>
+      <c r="B20" t="s">
         <v>443</v>
-      </c>
-      <c r="B20" t="s">
-        <v>444</v>
       </c>
       <c r="C20" t="n" s="5">
         <v>45952</v>
       </c>
       <c r="D20" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E20" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B21" t="s">
         <v>443</v>
-      </c>
-      <c r="B21" t="s">
-        <v>444</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>45912</v>
       </c>
       <c r="D21" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E21" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>442</v>
+      </c>
+      <c r="B22" t="s">
         <v>443</v>
-      </c>
-      <c r="B22" t="s">
-        <v>444</v>
       </c>
       <c r="C22" t="n" s="5">
         <v>45785</v>
       </c>
       <c r="D22" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E22" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -6884,13 +6890,13 @@
         <v>300</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>45785</v>
+        <v>45737</v>
       </c>
       <c r="D23" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E23" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -6901,13 +6907,13 @@
         <v>300</v>
       </c>
       <c r="C24" t="n" s="5">
-        <v>45737</v>
+        <v>45785</v>
       </c>
       <c r="D24" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E24" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -6921,10 +6927,10 @@
         <v>45834</v>
       </c>
       <c r="D25" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E25" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -6938,10 +6944,10 @@
         <v>45737</v>
       </c>
       <c r="D26" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E26" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -6955,10 +6961,10 @@
         <v>45785</v>
       </c>
       <c r="D27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E27" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -6972,10 +6978,10 @@
         <v>45785</v>
       </c>
       <c r="D28" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E28" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -6989,10 +6995,10 @@
         <v>45834</v>
       </c>
       <c r="D29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E29" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -7006,10 +7012,10 @@
         <v>45737</v>
       </c>
       <c r="D30" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E30" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -7023,10 +7029,10 @@
         <v>45785</v>
       </c>
       <c r="D31" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E31" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -7040,10 +7046,10 @@
         <v>45737</v>
       </c>
       <c r="D32" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E32" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -7057,10 +7063,10 @@
         <v>45737</v>
       </c>
       <c r="D33" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E33" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -7074,10 +7080,10 @@
         <v>45785</v>
       </c>
       <c r="D34" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E34" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -7091,129 +7097,129 @@
         <v>45737</v>
       </c>
       <c r="D35" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E35" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B36" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C36" t="n" s="5">
-        <v>45785</v>
+        <v>45930</v>
       </c>
       <c r="D36" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="E36" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B37" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C37" t="n" s="5">
-        <v>45910</v>
+        <v>45737</v>
       </c>
       <c r="D37" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E37" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B38" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C38" t="n" s="5">
-        <v>45930</v>
+        <v>45952</v>
       </c>
       <c r="D38" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E38" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B39" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C39" t="n" s="5">
-        <v>45737</v>
+        <v>45910</v>
       </c>
       <c r="D39" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="E39" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B40" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C40" t="n" s="5">
-        <v>45952</v>
+        <v>45785</v>
       </c>
       <c r="D40" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E40" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>451</v>
+      </c>
+      <c r="B41" t="s">
         <v>452</v>
-      </c>
-      <c r="B41" t="s">
-        <v>453</v>
       </c>
       <c r="C41" t="n" s="5">
         <v>45737</v>
       </c>
       <c r="D41" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E41" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B42" t="s">
         <v>452</v>
-      </c>
-      <c r="B42" t="s">
-        <v>453</v>
       </c>
       <c r="C42" t="n" s="5">
         <v>45749</v>
       </c>
       <c r="D42" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E42" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -7227,10 +7233,10 @@
         <v>45737</v>
       </c>
       <c r="D43" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E43" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -7244,10 +7250,10 @@
         <v>45737</v>
       </c>
       <c r="D44" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E44" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -7261,10 +7267,10 @@
         <v>45785</v>
       </c>
       <c r="D45" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E45" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -7278,10 +7284,10 @@
         <v>45737</v>
       </c>
       <c r="D46" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E46" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -7295,10 +7301,10 @@
         <v>45737</v>
       </c>
       <c r="D47" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E47" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -7312,15 +7318,15 @@
         <v>45737</v>
       </c>
       <c r="D48" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E48" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s">
         <v>333</v>
@@ -7329,15 +7335,15 @@
         <v>45749</v>
       </c>
       <c r="D49" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E49" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s">
         <v>333</v>
@@ -7346,10 +7352,10 @@
         <v>45757</v>
       </c>
       <c r="D50" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E50" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -7363,10 +7369,10 @@
         <v>45757</v>
       </c>
       <c r="D51" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E51" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -7380,10 +7386,10 @@
         <v>45824</v>
       </c>
       <c r="D52" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="E52" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -7394,13 +7400,13 @@
         <v>335</v>
       </c>
       <c r="C53" t="n" s="5">
-        <v>45834</v>
+        <v>45824</v>
       </c>
       <c r="D53" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="E53" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -7411,13 +7417,13 @@
         <v>335</v>
       </c>
       <c r="C54" t="n" s="5">
-        <v>45824</v>
+        <v>45834</v>
       </c>
       <c r="D54" t="s">
-        <v>619</v>
+        <v>641</v>
       </c>
       <c r="E54" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -7431,10 +7437,10 @@
         <v>45824</v>
       </c>
       <c r="D55" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="E55" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -7448,10 +7454,10 @@
         <v>45824</v>
       </c>
       <c r="D56" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E56" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -7465,10 +7471,10 @@
         <v>45824</v>
       </c>
       <c r="D57" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E57" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -7482,10 +7488,10 @@
         <v>45834</v>
       </c>
       <c r="D58" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E58" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -7499,10 +7505,10 @@
         <v>45824</v>
       </c>
       <c r="D59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E59" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -7516,10 +7522,10 @@
         <v>45824</v>
       </c>
       <c r="D60" t="s">
-        <v>616</v>
+        <v>644</v>
       </c>
       <c r="E60" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -7533,10 +7539,10 @@
         <v>45824</v>
       </c>
       <c r="D61" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E61" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -7550,10 +7556,10 @@
         <v>45824</v>
       </c>
       <c r="D62" t="s">
-        <v>642</v>
+        <v>618</v>
       </c>
       <c r="E62" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -7567,10 +7573,10 @@
         <v>45867</v>
       </c>
       <c r="D63" t="s">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="E63" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -7584,10 +7590,10 @@
         <v>45867</v>
       </c>
       <c r="D64" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E64" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -7601,10 +7607,10 @@
         <v>45867</v>
       </c>
       <c r="D65" t="s">
-        <v>643</v>
+        <v>618</v>
       </c>
       <c r="E65" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -7618,10 +7624,10 @@
         <v>45873</v>
       </c>
       <c r="D66" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E66" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -7635,10 +7641,10 @@
         <v>45867</v>
       </c>
       <c r="D67" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="E67" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -7652,10 +7658,10 @@
         <v>45867</v>
       </c>
       <c r="D68" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E68" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -7669,10 +7675,10 @@
         <v>45867</v>
       </c>
       <c r="D69" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E69" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -7686,112 +7692,112 @@
         <v>45867</v>
       </c>
       <c r="D70" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E70" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B71" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C71" t="n" s="5">
         <v>46224</v>
       </c>
       <c r="D71" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E71" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B72" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C72" t="n" s="5">
         <v>45867</v>
       </c>
       <c r="D72" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E72" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B73" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C73" t="n" s="5">
         <v>45867</v>
       </c>
       <c r="D73" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E73" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B74" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C74" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D74" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E74" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s">
         <v>355</v>
       </c>
       <c r="C75" t="n" s="5">
-        <v>45870</v>
+        <v>46031</v>
       </c>
       <c r="D75" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E75" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s">
         <v>355</v>
       </c>
       <c r="C76" t="n" s="5">
-        <v>46031</v>
+        <v>45870</v>
       </c>
       <c r="D76" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E76" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -7805,112 +7811,112 @@
         <v>45870</v>
       </c>
       <c r="D77" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E77" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B78" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C78" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D78" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E78" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B79" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C79" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D79" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E79" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B80" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C80" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D80" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E80" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B81" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C81" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D81" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E81" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>474</v>
+      </c>
+      <c r="B82" t="s">
         <v>475</v>
       </c>
-      <c r="B82" t="s">
-        <v>476</v>
-      </c>
       <c r="C82" t="n" s="5">
-        <v>45876</v>
+        <v>46188</v>
       </c>
       <c r="D82" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E82" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>474</v>
+      </c>
+      <c r="B83" t="s">
         <v>475</v>
       </c>
-      <c r="B83" t="s">
-        <v>476</v>
-      </c>
       <c r="C83" t="n" s="5">
-        <v>46188</v>
+        <v>45876</v>
       </c>
       <c r="D83" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E83" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -7924,10 +7930,10 @@
         <v>45939</v>
       </c>
       <c r="D84" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="E84" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -7941,10 +7947,10 @@
         <v>45939</v>
       </c>
       <c r="D85" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E85" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -7958,10 +7964,10 @@
         <v>45939</v>
       </c>
       <c r="D86" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="E86" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -7975,10 +7981,10 @@
         <v>45939</v>
       </c>
       <c r="D87" t="s">
-        <v>619</v>
+        <v>669</v>
       </c>
       <c r="E87" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -7992,10 +7998,10 @@
         <v>45939</v>
       </c>
       <c r="D88" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E88" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -8009,44 +8015,44 @@
         <v>45939</v>
       </c>
       <c r="D89" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E89" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B90" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C90" t="n" s="5">
         <v>46031</v>
       </c>
       <c r="D90" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="E90" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B91" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C91" t="n" s="5">
         <v>46033</v>
       </c>
       <c r="D91" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E91" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -8060,10 +8066,10 @@
         <v>46031</v>
       </c>
       <c r="D92" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E92" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -8077,10 +8083,10 @@
         <v>46031</v>
       </c>
       <c r="D93" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E93" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -8094,10 +8100,10 @@
         <v>46031</v>
       </c>
       <c r="D94" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E94" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -8111,10 +8117,10 @@
         <v>46031</v>
       </c>
       <c r="D95" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E95" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -8128,10 +8134,10 @@
         <v>46031</v>
       </c>
       <c r="D96" t="s">
-        <v>617</v>
+        <v>678</v>
       </c>
       <c r="E96" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -8145,10 +8151,10 @@
         <v>46031</v>
       </c>
       <c r="D97" t="s">
-        <v>676</v>
+        <v>619</v>
       </c>
       <c r="E97" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -8165,7 +8171,7 @@
         <v>618</v>
       </c>
       <c r="E98" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -8176,13 +8182,13 @@
         <v>297</v>
       </c>
       <c r="C99" t="n" s="5">
-        <v>46224</v>
+        <v>46031</v>
       </c>
       <c r="D99" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E99" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -8196,10 +8202,10 @@
         <v>46031</v>
       </c>
       <c r="D100" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E100" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -8213,10 +8219,10 @@
         <v>46031</v>
       </c>
       <c r="D101" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E101" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -8227,13 +8233,13 @@
         <v>297</v>
       </c>
       <c r="C102" t="n" s="5">
-        <v>46031</v>
+        <v>46224</v>
       </c>
       <c r="D102" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="E102" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -8247,10 +8253,10 @@
         <v>46031</v>
       </c>
       <c r="D103" t="s">
-        <v>679</v>
+        <v>621</v>
       </c>
       <c r="E103" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -8264,10 +8270,10 @@
         <v>46031</v>
       </c>
       <c r="D104" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E104" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -8281,10 +8287,10 @@
         <v>46031</v>
       </c>
       <c r="D105" t="s">
-        <v>619</v>
+        <v>681</v>
       </c>
       <c r="E105" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -8298,10 +8304,10 @@
         <v>46031</v>
       </c>
       <c r="D106" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E106" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -8315,10 +8321,10 @@
         <v>46031</v>
       </c>
       <c r="D107" t="s">
-        <v>680</v>
+        <v>624</v>
       </c>
       <c r="E107" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -8332,10 +8338,10 @@
         <v>46031</v>
       </c>
       <c r="D108" t="s">
-        <v>622</v>
+        <v>682</v>
       </c>
       <c r="E108" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -8349,10 +8355,10 @@
         <v>46031</v>
       </c>
       <c r="D109" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E109" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -8366,10 +8372,10 @@
         <v>46033</v>
       </c>
       <c r="D110" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E110" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -8383,10 +8389,10 @@
         <v>46033</v>
       </c>
       <c r="D111" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E111" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -8400,10 +8406,10 @@
         <v>46033</v>
       </c>
       <c r="D112" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E112" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -8417,10 +8423,10 @@
         <v>46033</v>
       </c>
       <c r="D113" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E113" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -8434,15 +8440,15 @@
         <v>46033</v>
       </c>
       <c r="D114" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E114" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B115" t="s">
         <v>316</v>
@@ -8451,15 +8457,15 @@
         <v>46033</v>
       </c>
       <c r="D115" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E115" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B116" t="s">
         <v>316</v>
@@ -8468,15 +8474,15 @@
         <v>46033</v>
       </c>
       <c r="D116" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E116" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B117" t="s">
         <v>316</v>
@@ -8485,10 +8491,10 @@
         <v>46279</v>
       </c>
       <c r="D117" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E117" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -8502,10 +8508,10 @@
         <v>46033</v>
       </c>
       <c r="D118" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="E118" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -8519,10 +8525,10 @@
         <v>46033</v>
       </c>
       <c r="D119" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="E119" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -8536,10 +8542,10 @@
         <v>46033</v>
       </c>
       <c r="D120" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E120" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -8553,10 +8559,10 @@
         <v>46033</v>
       </c>
       <c r="D121" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="E121" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -8570,10 +8576,10 @@
         <v>46033</v>
       </c>
       <c r="D122" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E122" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -8587,10 +8593,10 @@
         <v>46033</v>
       </c>
       <c r="D123" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="E123" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -8604,10 +8610,10 @@
         <v>46033</v>
       </c>
       <c r="D124" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E124" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -8621,10 +8627,10 @@
         <v>46033</v>
       </c>
       <c r="D125" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E125" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -8638,15 +8644,15 @@
         <v>46033</v>
       </c>
       <c r="D126" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E126" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B127" t="s">
         <v>344</v>
@@ -8655,15 +8661,15 @@
         <v>46033</v>
       </c>
       <c r="D127" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E127" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B128" t="s">
         <v>344</v>
@@ -8672,15 +8678,15 @@
         <v>46033</v>
       </c>
       <c r="D128" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E128" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B129" t="s">
         <v>344</v>
@@ -8689,15 +8695,15 @@
         <v>46033</v>
       </c>
       <c r="D129" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E129" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B130" t="s">
         <v>344</v>
@@ -8706,15 +8712,15 @@
         <v>46293</v>
       </c>
       <c r="D130" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E130" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B131" t="s">
         <v>344</v>
@@ -8723,10 +8729,10 @@
         <v>46248</v>
       </c>
       <c r="D131" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E131" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -8740,10 +8746,10 @@
         <v>46033</v>
       </c>
       <c r="D132" t="s">
-        <v>684</v>
+        <v>637</v>
       </c>
       <c r="E132" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -8757,44 +8763,44 @@
         <v>46033</v>
       </c>
       <c r="D133" t="s">
-        <v>635</v>
+        <v>686</v>
       </c>
       <c r="E133" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B134" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C134" t="n" s="5">
         <v>46066</v>
       </c>
       <c r="D134" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E134" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B135" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C135" t="n" s="5">
         <v>46153</v>
       </c>
       <c r="D135" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E135" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -8808,10 +8814,10 @@
         <v>46248</v>
       </c>
       <c r="D136" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E136" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -8825,10 +8831,10 @@
         <v>46283</v>
       </c>
       <c r="D137" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E137" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -8842,10 +8848,10 @@
         <v>46293</v>
       </c>
       <c r="D138" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E138" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -8859,10 +8865,10 @@
         <v>46293</v>
       </c>
       <c r="D139" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E139" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -8935,7 +8941,7 @@
         <v>237</v>
       </c>
       <c r="F2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G2" t="n" s="5">
         <v>45751</v>
@@ -8966,7 +8972,7 @@
         <v>237</v>
       </c>
       <c r="F3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G3" t="n" s="5">
         <v>45772</v>
@@ -8997,7 +9003,7 @@
         <v>237</v>
       </c>
       <c r="F4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G4" t="n" s="5">
         <v>45803</v>
@@ -9028,7 +9034,7 @@
         <v>237</v>
       </c>
       <c r="F5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G5" t="n" s="5">
         <v>46430</v>
@@ -9055,7 +9061,7 @@
         <v>237</v>
       </c>
       <c r="F6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G6" t="n" s="5">
         <v>46549</v>
@@ -9082,7 +9088,7 @@
         <v>237</v>
       </c>
       <c r="F7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G7" t="n" s="5">
         <v>45412</v>
@@ -9113,7 +9119,7 @@
         <v>237</v>
       </c>
       <c r="F8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G8" t="n" s="5">
         <v>45454</v>
@@ -9146,7 +9152,7 @@
         <v>237</v>
       </c>
       <c r="F9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G9" t="n" s="5">
         <v>45496</v>
@@ -9177,7 +9183,7 @@
         <v>237</v>
       </c>
       <c r="F10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G10" t="n" s="5">
         <v>45516</v>
@@ -9208,7 +9214,7 @@
         <v>237</v>
       </c>
       <c r="F11" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G11" t="n" s="5">
         <v>45545</v>
@@ -9239,7 +9245,7 @@
         <v>237</v>
       </c>
       <c r="F12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G12" t="n" s="5">
         <v>45686</v>
@@ -9270,7 +9276,7 @@
         <v>237</v>
       </c>
       <c r="F13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G13" t="n" s="5">
         <v>45719</v>
@@ -9301,7 +9307,7 @@
         <v>237</v>
       </c>
       <c r="F14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G14" t="n" s="5">
         <v>46470</v>
@@ -9328,7 +9334,7 @@
         <v>237</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G15" t="n" s="5">
         <v>46484</v>
@@ -9355,7 +9361,7 @@
         <v>237</v>
       </c>
       <c r="F16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G16" t="n" s="5">
         <v>46545</v>
@@ -9382,7 +9388,7 @@
         <v>237</v>
       </c>
       <c r="F17" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G17" t="n" s="5">
         <v>46574</v>
@@ -9409,7 +9415,7 @@
         <v>237</v>
       </c>
       <c r="F18" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G18" t="n" s="5">
         <v>46615</v>
@@ -9436,7 +9442,7 @@
         <v>237</v>
       </c>
       <c r="F19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G19" t="n" s="5">
         <v>46491</v>
@@ -9463,7 +9469,7 @@
         <v>237</v>
       </c>
       <c r="F20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G20" t="n" s="5">
         <v>46529</v>
@@ -9490,7 +9496,7 @@
         <v>237</v>
       </c>
       <c r="F21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G21" t="n" s="5">
         <v>46559</v>
@@ -9517,7 +9523,7 @@
         <v>237</v>
       </c>
       <c r="F22" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G22" t="n" s="5">
         <v>46587</v>
@@ -9544,7 +9550,7 @@
         <v>237</v>
       </c>
       <c r="F23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G23" t="n" s="5">
         <v>46617</v>
@@ -9571,7 +9577,7 @@
         <v>237</v>
       </c>
       <c r="F24" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G24" t="n" s="5">
         <v>46629</v>
@@ -9598,7 +9604,7 @@
         <v>237</v>
       </c>
       <c r="F25" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G25" t="n" s="5">
         <v>46657</v>
@@ -9625,7 +9631,7 @@
         <v>237</v>
       </c>
       <c r="F26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G26" t="n" s="5">
         <v>46686</v>
@@ -9652,7 +9658,7 @@
         <v>237</v>
       </c>
       <c r="F27" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G27" t="n" s="5">
         <v>46654</v>
@@ -9679,7 +9685,7 @@
         <v>237</v>
       </c>
       <c r="F28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G28" t="n" s="5">
         <v>46682</v>
@@ -9706,7 +9712,7 @@
         <v>237</v>
       </c>
       <c r="F29" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G29" t="n" s="5">
         <v>46710</v>
@@ -9733,7 +9739,7 @@
         <v>237</v>
       </c>
       <c r="F30" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G30" t="n" s="5">
         <v>46723</v>
@@ -9760,7 +9766,7 @@
         <v>237</v>
       </c>
       <c r="F31" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G31" t="n" s="5">
         <v>46742</v>
@@ -9787,7 +9793,7 @@
         <v>237</v>
       </c>
       <c r="F32" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G32" t="n" s="5">
         <v>46762</v>
@@ -9814,7 +9820,7 @@
         <v>237</v>
       </c>
       <c r="F33" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G33" t="n" s="5">
         <v>46784</v>
@@ -9841,7 +9847,7 @@
         <v>237</v>
       </c>
       <c r="F34" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G34" t="n" s="5">
         <v>46804</v>
@@ -9868,7 +9874,7 @@
         <v>237</v>
       </c>
       <c r="F35" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G35" t="n" s="5">
         <v>46477</v>
@@ -9895,7 +9901,7 @@
         <v>237</v>
       </c>
       <c r="F36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G36" t="n" s="5">
         <v>46505</v>
@@ -9922,7 +9928,7 @@
         <v>237</v>
       </c>
       <c r="F37" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G37" t="n" s="5">
         <v>46533</v>
@@ -9949,7 +9955,7 @@
         <v>237</v>
       </c>
       <c r="F38" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G38" t="n" s="5">
         <v>46546</v>
@@ -9976,7 +9982,7 @@
         <v>237</v>
       </c>
       <c r="F39" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G39" t="n" s="5">
         <v>46566</v>
@@ -10003,7 +10009,7 @@
         <v>237</v>
       </c>
       <c r="F40" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G40" t="n" s="5">
         <v>46587</v>
@@ -10030,7 +10036,7 @@
         <v>237</v>
       </c>
       <c r="F41" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G41" t="n" s="5">
         <v>46609</v>
@@ -10057,7 +10063,7 @@
         <v>237</v>
       </c>
       <c r="F42" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G42" t="n" s="5">
         <v>46629</v>
@@ -10084,7 +10090,7 @@
         <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G43" t="n" s="5">
         <v>45719</v>
@@ -10115,7 +10121,7 @@
         <v>237</v>
       </c>
       <c r="F44" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G44" t="n" s="5">
         <v>45740</v>
@@ -10146,7 +10152,7 @@
         <v>237</v>
       </c>
       <c r="F45" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G45" t="n" s="5">
         <v>45777</v>
@@ -10177,7 +10183,7 @@
         <v>237</v>
       </c>
       <c r="F46" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G46" t="n" s="5">
         <v>46440</v>
@@ -10208,7 +10214,7 @@
         <v>237</v>
       </c>
       <c r="F47" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G47" t="n" s="5">
         <v>46486</v>
@@ -10239,7 +10245,7 @@
         <v>237</v>
       </c>
       <c r="F48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G48" t="n" s="5">
         <v>46517</v>
@@ -10270,7 +10276,7 @@
         <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G49" t="n" s="5">
         <v>45919</v>
@@ -10301,7 +10307,7 @@
         <v>237</v>
       </c>
       <c r="F50" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G50" t="n" s="5">
         <v>45982</v>
@@ -10332,7 +10338,7 @@
         <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G51" t="n" s="5">
         <v>45824</v>
@@ -10363,7 +10369,7 @@
         <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G52" t="n" s="5">
         <v>45845</v>
@@ -10394,7 +10400,7 @@
         <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G53" t="n" s="5">
         <v>45847</v>
@@ -10425,7 +10431,7 @@
         <v>237</v>
       </c>
       <c r="F54" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G54" t="n" s="5">
         <v>45933</v>
@@ -10456,7 +10462,7 @@
         <v>237</v>
       </c>
       <c r="F55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G55" t="n" s="5">
         <v>45954</v>
@@ -10487,7 +10493,7 @@
         <v>237</v>
       </c>
       <c r="F56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G56" t="n" s="5">
         <v>45958</v>
@@ -10518,7 +10524,7 @@
         <v>237</v>
       </c>
       <c r="F57" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G57" t="n" s="5">
         <v>45856</v>
@@ -10549,7 +10555,7 @@
         <v>237</v>
       </c>
       <c r="F58" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G58" t="n" s="5">
         <v>45880</v>
@@ -10580,7 +10586,7 @@
         <v>237</v>
       </c>
       <c r="F59" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G59" t="n" s="5">
         <v>45901</v>
@@ -10611,7 +10617,7 @@
         <v>237</v>
       </c>
       <c r="F60" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G60" t="n" s="5">
         <v>45786</v>
@@ -10642,7 +10648,7 @@
         <v>237</v>
       </c>
       <c r="F61" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G61" t="n" s="5">
         <v>45803</v>
@@ -10673,7 +10679,7 @@
         <v>237</v>
       </c>
       <c r="F62" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G62" t="n" s="5">
         <v>45812</v>
@@ -10704,7 +10710,7 @@
         <v>237</v>
       </c>
       <c r="F63" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G63" t="n" s="5">
         <v>45856</v>
@@ -10735,7 +10741,7 @@
         <v>237</v>
       </c>
       <c r="F64" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G64" t="n" s="5">
         <v>45880</v>
@@ -10766,7 +10772,7 @@
         <v>237</v>
       </c>
       <c r="F65" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G65" t="n" s="5">
         <v>45901</v>
@@ -10797,7 +10803,7 @@
         <v>237</v>
       </c>
       <c r="F66" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G66" t="n" s="5">
         <v>45856</v>
@@ -10828,7 +10834,7 @@
         <v>237</v>
       </c>
       <c r="F67" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G67" t="n" s="5">
         <v>45880</v>
@@ -10859,7 +10865,7 @@
         <v>237</v>
       </c>
       <c r="F68" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G68" t="n" s="5">
         <v>45901</v>
@@ -10890,7 +10896,7 @@
         <v>237</v>
       </c>
       <c r="F69" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G69" t="n" s="5">
         <v>45856</v>
@@ -10921,7 +10927,7 @@
         <v>237</v>
       </c>
       <c r="F70" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G70" t="n" s="5">
         <v>45880</v>
@@ -10952,7 +10958,7 @@
         <v>237</v>
       </c>
       <c r="F71" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G71" t="n" s="5">
         <v>45901</v>
@@ -10983,7 +10989,7 @@
         <v>237</v>
       </c>
       <c r="F72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G72" t="n" s="5">
         <v>45730</v>
@@ -11014,7 +11020,7 @@
         <v>237</v>
       </c>
       <c r="F73" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G73" t="n" s="5">
         <v>45747</v>
@@ -11045,7 +11051,7 @@
         <v>237</v>
       </c>
       <c r="F74" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G74" t="n" s="5">
         <v>45772</v>
@@ -11076,7 +11082,7 @@
         <v>237</v>
       </c>
       <c r="F75" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G75" t="n" s="5">
         <v>45969</v>
@@ -11107,7 +11113,7 @@
         <v>237</v>
       </c>
       <c r="F76" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G76" t="n" s="5">
         <v>45994</v>
@@ -11138,7 +11144,7 @@
         <v>237</v>
       </c>
       <c r="F77" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G77" t="n" s="5">
         <v>46001</v>
@@ -11169,7 +11175,7 @@
         <v>237</v>
       </c>
       <c r="F78" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G78" t="n" s="5">
         <v>45779</v>
@@ -11200,7 +11206,7 @@
         <v>237</v>
       </c>
       <c r="F79" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G79" t="n" s="5">
         <v>45794</v>
@@ -11231,7 +11237,7 @@
         <v>237</v>
       </c>
       <c r="F80" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G80" t="n" s="5">
         <v>45825</v>
@@ -11262,7 +11268,7 @@
         <v>237</v>
       </c>
       <c r="F81" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G81" t="n" s="5">
         <v>45782</v>
@@ -11293,7 +11299,7 @@
         <v>237</v>
       </c>
       <c r="F82" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G82" t="n" s="5">
         <v>45796</v>
@@ -11324,7 +11330,7 @@
         <v>237</v>
       </c>
       <c r="F83" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G83" t="n" s="5">
         <v>45801</v>
@@ -11355,7 +11361,7 @@
         <v>237</v>
       </c>
       <c r="F84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G84" t="n" s="5">
         <v>45782</v>
@@ -11386,7 +11392,7 @@
         <v>237</v>
       </c>
       <c r="F85" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G85" t="n" s="5">
         <v>45824</v>
@@ -11417,7 +11423,7 @@
         <v>237</v>
       </c>
       <c r="F86" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G86" t="n" s="5">
         <v>45800</v>
@@ -11448,7 +11454,7 @@
         <v>237</v>
       </c>
       <c r="F87" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G87" t="n" s="5">
         <v>45814</v>
@@ -11479,7 +11485,7 @@
         <v>237</v>
       </c>
       <c r="F88" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G88" t="n" s="5">
         <v>45848</v>
@@ -11510,7 +11516,7 @@
         <v>237</v>
       </c>
       <c r="F89" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G89" t="n" s="5">
         <v>45800</v>
@@ -11541,7 +11547,7 @@
         <v>237</v>
       </c>
       <c r="F90" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G90" t="n" s="5">
         <v>45814</v>
@@ -11572,7 +11578,7 @@
         <v>237</v>
       </c>
       <c r="F91" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G91" t="n" s="5">
         <v>45848</v>
@@ -11603,7 +11609,7 @@
         <v>237</v>
       </c>
       <c r="F92" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G92" t="n" s="5">
         <v>46547</v>
@@ -11630,7 +11636,7 @@
         <v>237</v>
       </c>
       <c r="F93" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G93" t="n" s="5">
         <v>46559</v>
@@ -11657,7 +11663,7 @@
         <v>237</v>
       </c>
       <c r="F94" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G94" t="n" s="5">
         <v>46594</v>
@@ -11684,7 +11690,7 @@
         <v>237</v>
       </c>
       <c r="F95" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G95" t="n" s="5">
         <v>45763</v>
@@ -11715,7 +11721,7 @@
         <v>237</v>
       </c>
       <c r="F96" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G96" t="n" s="5">
         <v>45777</v>
@@ -11746,7 +11752,7 @@
         <v>237</v>
       </c>
       <c r="F97" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G97" t="n" s="5">
         <v>45800</v>
@@ -11777,7 +11783,7 @@
         <v>237</v>
       </c>
       <c r="F98" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G98" t="n" s="5">
         <v>45856</v>
@@ -11808,7 +11814,7 @@
         <v>237</v>
       </c>
       <c r="F99" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G99" t="n" s="5">
         <v>45880</v>
@@ -11839,7 +11845,7 @@
         <v>237</v>
       </c>
       <c r="F100" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G100" t="n" s="5">
         <v>45901</v>
@@ -11870,7 +11876,7 @@
         <v>237</v>
       </c>
       <c r="F101" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G101" t="n" s="5">
         <v>45856</v>
@@ -11901,7 +11907,7 @@
         <v>237</v>
       </c>
       <c r="F102" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G102" t="n" s="5">
         <v>45880</v>
@@ -11932,7 +11938,7 @@
         <v>237</v>
       </c>
       <c r="F103" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G103" t="n" s="5">
         <v>45901</v>
@@ -11963,7 +11969,7 @@
         <v>237</v>
       </c>
       <c r="F104" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G104" t="n" s="5">
         <v>45910</v>
@@ -11994,7 +12000,7 @@
         <v>237</v>
       </c>
       <c r="F105" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G105" t="n" s="5">
         <v>45925</v>
@@ -12025,7 +12031,7 @@
         <v>237</v>
       </c>
       <c r="F106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G106" t="n" s="5">
         <v>45954</v>
@@ -12056,7 +12062,7 @@
         <v>237</v>
       </c>
       <c r="F107" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G107" t="n" s="5">
         <v>45888</v>
@@ -12087,7 +12093,7 @@
         <v>237</v>
       </c>
       <c r="F108" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G108" t="n" s="5">
         <v>45903</v>
@@ -12118,7 +12124,7 @@
         <v>237</v>
       </c>
       <c r="F109" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G109" t="n" s="5">
         <v>45931</v>
@@ -12149,7 +12155,7 @@
         <v>237</v>
       </c>
       <c r="F110" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G110" t="n" s="5">
         <v>45887</v>
@@ -12180,7 +12186,7 @@
         <v>237</v>
       </c>
       <c r="F111" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G111" t="n" s="5">
         <v>45932</v>
@@ -12213,7 +12219,7 @@
         <v>237</v>
       </c>
       <c r="F112" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G112" t="n" s="5">
         <v>45961</v>
@@ -12244,7 +12250,7 @@
         <v>237</v>
       </c>
       <c r="F113" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G113" t="n" s="5">
         <v>46006</v>
@@ -12275,7 +12281,7 @@
         <v>237</v>
       </c>
       <c r="F114" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G114" t="n" s="5">
         <v>46036</v>
@@ -12306,7 +12312,7 @@
         <v>237</v>
       </c>
       <c r="F115" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G115" t="n" s="5">
         <v>45923</v>
@@ -12337,7 +12343,7 @@
         <v>237</v>
       </c>
       <c r="F116" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G116" t="n" s="5">
         <v>45934</v>
@@ -12368,7 +12374,7 @@
         <v>237</v>
       </c>
       <c r="F117" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G117" t="n" s="5">
         <v>45955</v>
@@ -12399,7 +12405,7 @@
         <v>237</v>
       </c>
       <c r="F118" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G118" t="n" s="5">
         <v>45964</v>
@@ -12430,7 +12436,7 @@
         <v>237</v>
       </c>
       <c r="F119" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G119" t="n" s="5">
         <v>45975</v>
@@ -12461,7 +12467,7 @@
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G120" t="n" s="5">
         <v>46006</v>
@@ -12492,7 +12498,7 @@
         <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G121" t="n" s="5">
         <v>45919</v>
@@ -12523,7 +12529,7 @@
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G122" t="n" s="5">
         <v>45936</v>
@@ -12554,7 +12560,7 @@
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G123" t="n" s="5">
         <v>45971</v>
@@ -12585,7 +12591,7 @@
         <v>358</v>
       </c>
       <c r="F124" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G124" t="n" s="5">
         <v>45909</v>
@@ -12614,7 +12620,7 @@
         <v>358</v>
       </c>
       <c r="F125" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G125" t="n" s="5">
         <v>45930</v>
@@ -12643,7 +12649,7 @@
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G126" t="n" s="5">
         <v>45972</v>
@@ -12674,7 +12680,7 @@
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G127" t="n" s="5">
         <v>45979</v>
@@ -12705,7 +12711,7 @@
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G128" t="n" s="5">
         <v>46007</v>
@@ -12736,7 +12742,7 @@
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G129" t="n" s="5">
         <v>45968</v>
@@ -12767,7 +12773,7 @@
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G130" t="n" s="5">
         <v>45975</v>
@@ -12798,7 +12804,7 @@
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G131" t="n" s="5">
         <v>46006</v>
@@ -12829,7 +12835,7 @@
         <v>358</v>
       </c>
       <c r="F132" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G132" t="n" s="5">
         <v>46172</v>
@@ -12858,7 +12864,7 @@
         <v>358</v>
       </c>
       <c r="F133" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G133" t="n" s="5">
         <v>46200</v>
@@ -12885,7 +12891,7 @@
         <v>237</v>
       </c>
       <c r="F134" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G134" t="n" s="5">
         <v>46038</v>
@@ -12914,7 +12920,7 @@
         <v>237</v>
       </c>
       <c r="F135" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G135" t="n" s="5">
         <v>46073</v>
@@ -12941,7 +12947,7 @@
         <v>237</v>
       </c>
       <c r="F136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G136" t="n" s="5">
         <v>46125</v>
@@ -12972,7 +12978,7 @@
         <v>237</v>
       </c>
       <c r="F137" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G137" t="n" s="5">
         <v>46146</v>
@@ -13003,7 +13009,7 @@
         <v>237</v>
       </c>
       <c r="F138" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G138" t="n" s="5">
         <v>46174</v>
@@ -13034,7 +13040,7 @@
         <v>237</v>
       </c>
       <c r="F139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G139" t="n" s="5">
         <v>46231</v>
@@ -13065,7 +13071,7 @@
         <v>237</v>
       </c>
       <c r="F140" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G140" t="n" s="5">
         <v>46252</v>
@@ -13096,7 +13102,7 @@
         <v>237</v>
       </c>
       <c r="F141" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G141" t="n" s="5">
         <v>46280</v>
@@ -13127,7 +13133,7 @@
         <v>237</v>
       </c>
       <c r="F142" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G142" t="n" s="5">
         <v>46227</v>
@@ -13158,7 +13164,7 @@
         <v>237</v>
       </c>
       <c r="F143" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G143" t="n" s="5">
         <v>46241</v>
@@ -13189,7 +13195,7 @@
         <v>237</v>
       </c>
       <c r="F144" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G144" t="n" s="5">
         <v>46262</v>
@@ -13220,7 +13226,7 @@
         <v>237</v>
       </c>
       <c r="F145" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G145" t="n" s="5">
         <v>46125</v>
@@ -13251,7 +13257,7 @@
         <v>237</v>
       </c>
       <c r="F146" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G146" t="n" s="5">
         <v>46146</v>
@@ -13282,7 +13288,7 @@
         <v>237</v>
       </c>
       <c r="F147" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G147" t="n" s="5">
         <v>46174</v>
@@ -13313,7 +13319,7 @@
         <v>237</v>
       </c>
       <c r="F148" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G148" t="n" s="5">
         <v>46183</v>
@@ -13344,7 +13350,7 @@
         <v>237</v>
       </c>
       <c r="F149" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G149" t="n" s="5">
         <v>46233</v>
@@ -13375,7 +13381,7 @@
         <v>237</v>
       </c>
       <c r="F150" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G150" t="n" s="5">
         <v>46262</v>
@@ -13406,7 +13412,7 @@
         <v>237</v>
       </c>
       <c r="F151" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G151" t="n" s="5">
         <v>46170</v>
@@ -13437,7 +13443,7 @@
         <v>237</v>
       </c>
       <c r="F152" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G152" t="n" s="5">
         <v>46185</v>
@@ -13468,7 +13474,7 @@
         <v>237</v>
       </c>
       <c r="F153" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G153" t="n" s="5">
         <v>46216</v>
@@ -13499,7 +13505,7 @@
         <v>237</v>
       </c>
       <c r="F154" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G154" t="n" s="5">
         <v>46227</v>
@@ -13530,7 +13536,7 @@
         <v>237</v>
       </c>
       <c r="F155" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G155" t="n" s="5">
         <v>46240</v>
@@ -13561,7 +13567,7 @@
         <v>237</v>
       </c>
       <c r="F156" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G156" t="n" s="5">
         <v>46262</v>
@@ -13577,7 +13583,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B157" t="s">
         <v>316</v>
@@ -13592,7 +13598,7 @@
         <v>237</v>
       </c>
       <c r="F157" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G157" t="n" s="5">
         <v>46230</v>
@@ -13608,7 +13614,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B158" t="s">
         <v>316</v>
@@ -13623,7 +13629,7 @@
         <v>237</v>
       </c>
       <c r="F158" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G158" t="n" s="5">
         <v>46255</v>
@@ -13639,7 +13645,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B159" t="s">
         <v>316</v>
@@ -13654,7 +13660,7 @@
         <v>237</v>
       </c>
       <c r="F159" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G159" t="n" s="5">
         <v>46283</v>
@@ -13683,7 +13689,7 @@
         <v>237</v>
       </c>
       <c r="F160" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G160" t="n" s="5">
         <v>46119</v>
@@ -13714,7 +13720,7 @@
         <v>237</v>
       </c>
       <c r="F161" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G161" t="n" s="5">
         <v>46129</v>
@@ -13745,7 +13751,7 @@
         <v>237</v>
       </c>
       <c r="F162" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G162" t="n" s="5">
         <v>46160</v>
@@ -13776,7 +13782,7 @@
         <v>237</v>
       </c>
       <c r="F163" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G163" t="n" s="5">
         <v>46202</v>
@@ -13807,7 +13813,7 @@
         <v>237</v>
       </c>
       <c r="F164" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G164" t="n" s="5">
         <v>46232</v>
@@ -13838,7 +13844,7 @@
         <v>237</v>
       </c>
       <c r="F165" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G165" t="n" s="5">
         <v>46262</v>
@@ -13869,12 +13875,14 @@
         <v>237</v>
       </c>
       <c r="F166" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G166" t="n" s="5">
         <v>46272</v>
       </c>
-      <c r="H166" s="5"/>
+      <c r="H166" t="n" s="5">
+        <v>46272</v>
+      </c>
       <c r="I166" t="n" s="5">
         <v>46287</v>
       </c>
@@ -13898,13 +13906,17 @@
         <v>237</v>
       </c>
       <c r="F167" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G167" t="n" s="5">
         <v>46283</v>
       </c>
-      <c r="H167" s="5"/>
-      <c r="I167" s="5"/>
+      <c r="H167" t="n" s="5">
+        <v>46283</v>
+      </c>
+      <c r="I167" t="n" s="5">
+        <v>46308</v>
+      </c>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
     </row>
@@ -13925,19 +13937,21 @@
         <v>237</v>
       </c>
       <c r="F168" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G168" t="n" s="5">
         <v>46314</v>
       </c>
-      <c r="H168" s="5"/>
+      <c r="H168" t="n" s="5">
+        <v>46314</v>
+      </c>
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B169" t="s">
         <v>344</v>
@@ -13952,7 +13966,7 @@
         <v>237</v>
       </c>
       <c r="F169" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G169" t="n" s="5">
         <v>46304</v>
@@ -13964,7 +13978,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B170" t="s">
         <v>344</v>
@@ -13979,7 +13993,7 @@
         <v>237</v>
       </c>
       <c r="F170" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G170" t="n" s="5">
         <v>46316</v>
@@ -13991,7 +14005,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B171" t="s">
         <v>344</v>
@@ -14006,7 +14020,7 @@
         <v>237</v>
       </c>
       <c r="F171" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G171" t="n" s="5">
         <v>46349</v>
@@ -14033,13 +14047,15 @@
         <v>237</v>
       </c>
       <c r="F172" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G172" t="n" s="5">
         <v>46297</v>
       </c>
       <c r="H172" s="5"/>
-      <c r="I172" s="5"/>
+      <c r="I172" t="n" s="5">
+        <v>46308</v>
+      </c>
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
     </row>
@@ -14060,7 +14076,7 @@
         <v>237</v>
       </c>
       <c r="F173" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G173" t="n" s="5">
         <v>46310</v>
@@ -14087,7 +14103,7 @@
         <v>237</v>
       </c>
       <c r="F174" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G174" t="n" s="5">
         <v>46342</v>
@@ -14114,7 +14130,7 @@
         <v>237</v>
       </c>
       <c r="F175" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G175" t="n" s="5">
         <v>46094</v>
@@ -14143,7 +14159,7 @@
         <v>237</v>
       </c>
       <c r="F176" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G176" t="n" s="5">
         <v>46142</v>
@@ -14172,7 +14188,7 @@
         <v>237</v>
       </c>
       <c r="F177" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G177" t="n" s="5">
         <v>46354</v>
@@ -14199,7 +14215,7 @@
         <v>237</v>
       </c>
       <c r="F178" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G178" t="n" s="5">
         <v>46367</v>
@@ -14226,7 +14242,7 @@
         <v>237</v>
       </c>
       <c r="F179" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G179" t="n" s="5">
         <v>46409</v>
@@ -14253,7 +14269,7 @@
         <v>237</v>
       </c>
       <c r="F180" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G180" t="n" s="5">
         <v>46310</v>
@@ -14280,7 +14296,7 @@
         <v>237</v>
       </c>
       <c r="F181" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G181" t="n" s="5">
         <v>46322</v>
@@ -14307,7 +14323,7 @@
         <v>237</v>
       </c>
       <c r="F182" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G182" t="n" s="5">
         <v>46353</v>
@@ -14334,7 +14350,7 @@
         <v>237</v>
       </c>
       <c r="F183" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G183" t="n" s="5">
         <v>46325</v>
@@ -14361,7 +14377,7 @@
         <v>237</v>
       </c>
       <c r="F184" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G184" t="n" s="5">
         <v>46337</v>
@@ -14388,7 +14404,7 @@
         <v>237</v>
       </c>
       <c r="F185" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G185" t="n" s="5">
         <v>46367</v>
@@ -14405,7 +14421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0017DABE-EE5D-40E5-AE1B-EB23E2085E81}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
@@ -14461,23 +14477,23 @@
         <v>233</v>
       </c>
       <c r="C2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D2" t="s">
         <v>430</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>431</v>
-      </c>
-      <c r="E2" t="s">
-        <v>432</v>
       </c>
       <c r="F2" t="n" s="3">
         <v>429382.89</v>
       </c>
       <c r="G2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2"/>
       <c r="I2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -14491,23 +14507,23 @@
         <v>247</v>
       </c>
       <c r="C3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D3" t="s">
+        <v>430</v>
+      </c>
+      <c r="E3" t="s">
         <v>431</v>
-      </c>
-      <c r="E3" t="s">
-        <v>432</v>
       </c>
       <c r="F3" t="n" s="3">
         <v>194232024.02</v>
       </c>
       <c r="G3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
@@ -14521,23 +14537,23 @@
         <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E4" t="s">
         <v>431</v>
-      </c>
-      <c r="E4" t="s">
-        <v>432</v>
       </c>
       <c r="F4" t="n" s="3">
         <v>20493161.89</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -14551,23 +14567,23 @@
         <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E5" t="s">
         <v>431</v>
-      </c>
-      <c r="E5" t="s">
-        <v>432</v>
       </c>
       <c r="F5" t="n" s="3">
         <v>633847.5</v>
       </c>
       <c r="G5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J5"/>
       <c r="K5"/>
@@ -14581,23 +14597,23 @@
         <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E6" t="s">
         <v>431</v>
-      </c>
-      <c r="E6" t="s">
-        <v>432</v>
       </c>
       <c r="F6" t="n" s="3">
         <v>225677</v>
       </c>
       <c r="G6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -14611,23 +14627,23 @@
         <v>288</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E7" t="s">
         <v>431</v>
-      </c>
-      <c r="E7" t="s">
-        <v>432</v>
       </c>
       <c r="F7" t="n" s="3">
         <v>96000</v>
       </c>
       <c r="G7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J7"/>
       <c r="K7"/>
@@ -14641,23 +14657,23 @@
         <v>294</v>
       </c>
       <c r="C8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D8" t="s">
+        <v>430</v>
+      </c>
+      <c r="E8" t="s">
         <v>431</v>
-      </c>
-      <c r="E8" t="s">
-        <v>432</v>
       </c>
       <c r="F8" t="n" s="3">
         <v>72000</v>
       </c>
       <c r="G8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -14671,23 +14687,23 @@
         <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E9" t="s">
         <v>431</v>
-      </c>
-      <c r="E9" t="s">
-        <v>432</v>
       </c>
       <c r="F9" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J9"/>
       <c r="K9"/>
@@ -14695,29 +14711,29 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" t="s">
         <v>443</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>444</v>
       </c>
-      <c r="C10" t="s">
-        <v>445</v>
-      </c>
       <c r="D10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E10" t="s">
         <v>431</v>
-      </c>
-      <c r="E10" t="s">
-        <v>432</v>
       </c>
       <c r="F10" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -14731,23 +14747,23 @@
         <v>300</v>
       </c>
       <c r="C11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D11" t="s">
+        <v>430</v>
+      </c>
+      <c r="E11" t="s">
         <v>431</v>
-      </c>
-      <c r="E11" t="s">
-        <v>432</v>
       </c>
       <c r="F11" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H11"/>
       <c r="I11" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J11"/>
       <c r="K11"/>
@@ -14761,23 +14777,23 @@
         <v>303</v>
       </c>
       <c r="C12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D12" t="s">
+        <v>430</v>
+      </c>
+      <c r="E12" t="s">
         <v>431</v>
-      </c>
-      <c r="E12" t="s">
-        <v>432</v>
       </c>
       <c r="F12" t="n" s="3">
         <v>42000</v>
       </c>
       <c r="G12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H12"/>
       <c r="I12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -14791,23 +14807,23 @@
         <v>306</v>
       </c>
       <c r="C13" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D13" t="s">
+        <v>430</v>
+      </c>
+      <c r="E13" t="s">
         <v>431</v>
-      </c>
-      <c r="E13" t="s">
-        <v>432</v>
       </c>
       <c r="F13" t="n" s="3">
         <v>72000</v>
       </c>
       <c r="G13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H13"/>
       <c r="I13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J13"/>
       <c r="K13"/>
@@ -14821,23 +14837,23 @@
         <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" t="s">
         <v>431</v>
-      </c>
-      <c r="E14" t="s">
-        <v>432</v>
       </c>
       <c r="F14" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H14"/>
       <c r="I14" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J14"/>
       <c r="K14"/>
@@ -14851,19 +14867,19 @@
         <v>312</v>
       </c>
       <c r="C15" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="3"/>
       <c r="G15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H15"/>
       <c r="I15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J15"/>
       <c r="K15"/>
@@ -14877,23 +14893,23 @@
         <v>316</v>
       </c>
       <c r="C16" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D16" t="s">
+        <v>430</v>
+      </c>
+      <c r="E16" t="s">
         <v>431</v>
-      </c>
-      <c r="E16" t="s">
-        <v>432</v>
       </c>
       <c r="F16" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H16"/>
       <c r="I16" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J16"/>
       <c r="K16"/>
@@ -14901,25 +14917,25 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>451</v>
+      </c>
+      <c r="B17" t="s">
         <v>452</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>453</v>
       </c>
-      <c r="C17" t="s">
-        <v>454</v>
-      </c>
       <c r="D17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H17"/>
       <c r="I17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J17"/>
       <c r="K17"/>
@@ -14933,19 +14949,19 @@
         <v>319</v>
       </c>
       <c r="C18" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="3"/>
       <c r="G18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H18"/>
       <c r="I18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J18"/>
       <c r="K18"/>
@@ -14959,23 +14975,23 @@
         <v>321</v>
       </c>
       <c r="C19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D19" t="s">
+        <v>430</v>
+      </c>
+      <c r="E19" t="s">
         <v>431</v>
-      </c>
-      <c r="E19" t="s">
-        <v>432</v>
       </c>
       <c r="F19" t="n" s="3">
         <v>96000</v>
       </c>
       <c r="G19" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H19"/>
       <c r="I19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J19"/>
       <c r="K19"/>
@@ -14989,23 +15005,23 @@
         <v>323</v>
       </c>
       <c r="C20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D20" t="s">
+        <v>430</v>
+      </c>
+      <c r="E20" t="s">
         <v>431</v>
-      </c>
-      <c r="E20" t="s">
-        <v>432</v>
       </c>
       <c r="F20" t="n" s="3">
         <v>187475</v>
       </c>
       <c r="G20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H20"/>
       <c r="I20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J20"/>
       <c r="K20"/>
@@ -15019,19 +15035,19 @@
         <v>326</v>
       </c>
       <c r="C21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="3"/>
       <c r="G21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H21"/>
       <c r="I21" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J21"/>
       <c r="K21"/>
@@ -15045,19 +15061,19 @@
         <v>328</v>
       </c>
       <c r="C22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="3"/>
       <c r="G22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H22"/>
       <c r="I22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
@@ -15065,25 +15081,25 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B23" t="s">
         <v>333</v>
       </c>
       <c r="C23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="3"/>
       <c r="G23" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H23"/>
       <c r="I23" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J23"/>
       <c r="K23"/>
@@ -15097,19 +15113,19 @@
         <v>333</v>
       </c>
       <c r="C24" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="3"/>
       <c r="G24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H24"/>
       <c r="I24" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J24"/>
       <c r="K24"/>
@@ -15123,23 +15139,23 @@
         <v>335</v>
       </c>
       <c r="C25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D25" t="s">
+        <v>430</v>
+      </c>
+      <c r="E25" t="s">
         <v>431</v>
-      </c>
-      <c r="E25" t="s">
-        <v>432</v>
       </c>
       <c r="F25" t="n" s="3">
         <v>92400</v>
       </c>
       <c r="G25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H25"/>
       <c r="I25" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J25"/>
       <c r="K25"/>
@@ -15153,23 +15169,23 @@
         <v>338</v>
       </c>
       <c r="C26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
+        <v>430</v>
+      </c>
+      <c r="E26" t="s">
         <v>431</v>
-      </c>
-      <c r="E26" t="s">
-        <v>432</v>
       </c>
       <c r="F26" t="n" s="3">
         <v>44400</v>
       </c>
       <c r="G26" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J26"/>
       <c r="K26"/>
@@ -15183,23 +15199,23 @@
         <v>341</v>
       </c>
       <c r="C27" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D27" t="s">
+        <v>430</v>
+      </c>
+      <c r="E27" t="s">
         <v>431</v>
-      </c>
-      <c r="E27" t="s">
-        <v>432</v>
       </c>
       <c r="F27" t="n" s="3">
         <v>66000</v>
       </c>
       <c r="G27" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
@@ -15213,23 +15229,23 @@
         <v>344</v>
       </c>
       <c r="C28" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D28" t="s">
+        <v>430</v>
+      </c>
+      <c r="E28" t="s">
         <v>431</v>
-      </c>
-      <c r="E28" t="s">
-        <v>432</v>
       </c>
       <c r="F28" t="n" s="3">
         <v>63360</v>
       </c>
       <c r="G28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J28"/>
       <c r="K28"/>
@@ -15243,29 +15259,29 @@
         <v>347</v>
       </c>
       <c r="C29" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D29" t="s">
+        <v>430</v>
+      </c>
+      <c r="E29" t="s">
         <v>431</v>
-      </c>
-      <c r="E29" t="s">
-        <v>432</v>
       </c>
       <c r="F29" t="n" s="3">
         <v>3188838.4</v>
       </c>
       <c r="G29" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H29"/>
       <c r="I29" t="s">
+        <v>465</v>
+      </c>
+      <c r="J29" t="s">
         <v>466</v>
       </c>
-      <c r="J29" t="s">
-        <v>467</v>
-      </c>
       <c r="K29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L29"/>
     </row>
@@ -15277,29 +15293,29 @@
         <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D30" t="s">
+        <v>430</v>
+      </c>
+      <c r="E30" t="s">
         <v>431</v>
-      </c>
-      <c r="E30" t="s">
-        <v>432</v>
       </c>
       <c r="F30" t="n" s="3">
         <v>3188838.4</v>
       </c>
       <c r="G30" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H30"/>
       <c r="I30" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J30" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K30" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L30"/>
     </row>
@@ -15311,19 +15327,19 @@
         <v>351</v>
       </c>
       <c r="C31" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="3"/>
       <c r="G31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J31"/>
       <c r="K31"/>
@@ -15337,19 +15353,19 @@
         <v>351</v>
       </c>
       <c r="C32" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="3"/>
       <c r="G32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J32"/>
       <c r="K32"/>
@@ -15357,25 +15373,25 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B33" t="s">
         <v>355</v>
       </c>
       <c r="C33" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D33" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="3"/>
       <c r="G33" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H33"/>
       <c r="I33" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J33"/>
       <c r="K33"/>
@@ -15389,19 +15405,19 @@
         <v>354</v>
       </c>
       <c r="C34" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D34" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="3"/>
       <c r="G34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H34"/>
       <c r="I34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J34"/>
       <c r="K34"/>
@@ -15415,23 +15431,23 @@
         <v>357</v>
       </c>
       <c r="C35" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D35" t="s">
+        <v>430</v>
+      </c>
+      <c r="E35" t="s">
         <v>431</v>
-      </c>
-      <c r="E35" t="s">
-        <v>432</v>
       </c>
       <c r="F35" t="n" s="3">
         <v>229392.84</v>
       </c>
       <c r="G35" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H35"/>
       <c r="I35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J35"/>
       <c r="K35"/>
@@ -15439,25 +15455,25 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>474</v>
+      </c>
+      <c r="B36" t="s">
         <v>475</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>476</v>
       </c>
-      <c r="C36" t="s">
-        <v>477</v>
-      </c>
       <c r="D36" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="3"/>
       <c r="G36" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H36"/>
       <c r="I36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J36"/>
       <c r="K36"/>
@@ -15471,19 +15487,19 @@
         <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D37" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="3"/>
       <c r="G37" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H37"/>
       <c r="I37" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J37"/>
       <c r="K37"/>
@@ -15497,19 +15513,19 @@
         <v>326</v>
       </c>
       <c r="C38" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D38" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E38"/>
       <c r="F38" s="3"/>
       <c r="G38" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H38"/>
       <c r="I38" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J38"/>
       <c r="K38"/>
@@ -15523,23 +15539,23 @@
         <v>288</v>
       </c>
       <c r="C39" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D39" t="s">
+        <v>430</v>
+      </c>
+      <c r="E39" t="s">
         <v>431</v>
-      </c>
-      <c r="E39" t="s">
-        <v>432</v>
       </c>
       <c r="F39" t="n" s="3">
         <v>96000</v>
       </c>
       <c r="G39" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H39"/>
       <c r="I39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J39"/>
       <c r="K39"/>
@@ -15553,23 +15569,23 @@
         <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D40" t="s">
+        <v>430</v>
+      </c>
+      <c r="E40" t="s">
         <v>431</v>
-      </c>
-      <c r="E40" t="s">
-        <v>432</v>
       </c>
       <c r="F40" t="n" s="3">
         <v>72000</v>
       </c>
       <c r="G40" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H40"/>
       <c r="I40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J40"/>
       <c r="K40"/>
@@ -15583,23 +15599,23 @@
         <v>297</v>
       </c>
       <c r="C41" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D41" t="s">
+        <v>430</v>
+      </c>
+      <c r="E41" t="s">
         <v>431</v>
-      </c>
-      <c r="E41" t="s">
-        <v>432</v>
       </c>
       <c r="F41" t="n" s="3">
         <v>72000</v>
       </c>
       <c r="G41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H41"/>
       <c r="I41" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J41"/>
       <c r="K41"/>
@@ -15613,23 +15629,23 @@
         <v>300</v>
       </c>
       <c r="C42" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D42" t="s">
+        <v>430</v>
+      </c>
+      <c r="E42" t="s">
         <v>431</v>
-      </c>
-      <c r="E42" t="s">
-        <v>432</v>
       </c>
       <c r="F42" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G42" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J42"/>
       <c r="K42"/>
@@ -15643,23 +15659,23 @@
         <v>303</v>
       </c>
       <c r="C43" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D43" t="s">
+        <v>430</v>
+      </c>
+      <c r="E43" t="s">
         <v>431</v>
-      </c>
-      <c r="E43" t="s">
-        <v>432</v>
       </c>
       <c r="F43" t="n" s="3">
         <v>36000</v>
       </c>
       <c r="G43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J43"/>
       <c r="K43"/>
@@ -15673,23 +15689,23 @@
         <v>306</v>
       </c>
       <c r="C44" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D44" t="s">
+        <v>430</v>
+      </c>
+      <c r="E44" t="s">
         <v>431</v>
-      </c>
-      <c r="E44" t="s">
-        <v>432</v>
       </c>
       <c r="F44" t="n" s="3">
         <v>72000</v>
       </c>
       <c r="G44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J44"/>
       <c r="K44"/>
@@ -15703,23 +15719,23 @@
         <v>309</v>
       </c>
       <c r="C45" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D45" t="s">
+        <v>430</v>
+      </c>
+      <c r="E45" t="s">
         <v>431</v>
-      </c>
-      <c r="E45" t="s">
-        <v>432</v>
       </c>
       <c r="F45" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G45" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J45"/>
       <c r="K45"/>
@@ -15727,29 +15743,29 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s">
         <v>316</v>
       </c>
       <c r="C46" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D46" t="s">
+        <v>430</v>
+      </c>
+      <c r="E46" t="s">
         <v>431</v>
-      </c>
-      <c r="E46" t="s">
-        <v>432</v>
       </c>
       <c r="F46" t="n" s="3">
         <v>60000</v>
       </c>
       <c r="G46" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H46"/>
       <c r="I46" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J46"/>
       <c r="K46"/>
@@ -15763,23 +15779,23 @@
         <v>321</v>
       </c>
       <c r="C47" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D47" t="s">
+        <v>430</v>
+      </c>
+      <c r="E47" t="s">
         <v>431</v>
-      </c>
-      <c r="E47" t="s">
-        <v>432</v>
       </c>
       <c r="F47" t="n" s="3">
         <v>96000</v>
       </c>
       <c r="G47" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H47"/>
       <c r="I47" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J47"/>
       <c r="K47"/>
@@ -15793,23 +15809,23 @@
         <v>335</v>
       </c>
       <c r="C48" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D48" t="s">
+        <v>430</v>
+      </c>
+      <c r="E48" t="s">
         <v>431</v>
-      </c>
-      <c r="E48" t="s">
-        <v>432</v>
       </c>
       <c r="F48" t="n" s="3">
         <v>92400</v>
       </c>
       <c r="G48" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J48"/>
       <c r="K48"/>
@@ -15817,33 +15833,59 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="C49" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="D49" t="s">
-        <v>431</v>
-      </c>
-      <c r="E49" t="s">
+        <v>430</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49" s="3"/>
+      <c r="G49" t="s">
         <v>432</v>
-      </c>
-      <c r="F49" t="n" s="3">
-        <v>249600</v>
-      </c>
-      <c r="G49" t="s">
-        <v>433</v>
       </c>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J49"/>
       <c r="K49"/>
       <c r="L49"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" t="s">
+        <v>370</v>
+      </c>
+      <c r="C50" t="s">
+        <v>456</v>
+      </c>
+      <c r="D50" t="s">
+        <v>430</v>
+      </c>
+      <c r="E50" t="s">
+        <v>431</v>
+      </c>
+      <c r="F50" t="n" s="3">
+        <v>249600</v>
+      </c>
+      <c r="G50" t="s">
+        <v>432</v>
+      </c>
+      <c r="H50"/>
+      <c r="I50" t="s">
+        <v>435</v>
+      </c>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15952,10 +15994,10 @@
         <v>234</v>
       </c>
       <c r="E2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F2" t="s">
         <v>430</v>
-      </c>
-      <c r="F2" t="s">
-        <v>431</v>
       </c>
       <c r="G2" t="s">
         <v>482</v>
@@ -15979,7 +16021,7 @@
         <v>21001</v>
       </c>
       <c r="N2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O2"/>
       <c r="P2"/>
@@ -16008,10 +16050,10 @@
         <v>248</v>
       </c>
       <c r="E3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G3" t="s">
         <v>482</v>
@@ -16035,7 +16077,7 @@
         <v>10104</v>
       </c>
       <c r="N3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O3"/>
       <c r="P3"/>
@@ -16064,10 +16106,10 @@
         <v>272</v>
       </c>
       <c r="E4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G4" t="s">
         <v>491</v>
@@ -16091,7 +16133,7 @@
         <v>21001</v>
       </c>
       <c r="N4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O4"/>
       <c r="P4"/>
@@ -16120,10 +16162,10 @@
         <v>278</v>
       </c>
       <c r="E5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G5" t="s">
         <v>491</v>
@@ -16147,7 +16189,7 @@
         <v>10104</v>
       </c>
       <c r="N5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O5"/>
       <c r="P5"/>
@@ -16176,10 +16218,10 @@
         <v>284</v>
       </c>
       <c r="E6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G6" t="s">
         <v>491</v>
@@ -16203,7 +16245,7 @@
         <v>10104</v>
       </c>
       <c r="N6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O6"/>
       <c r="P6"/>
@@ -16232,10 +16274,10 @@
         <v>289</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G7" t="s">
         <v>502</v>
@@ -16259,7 +16301,7 @@
         <v>10103</v>
       </c>
       <c r="N7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O7"/>
       <c r="P7"/>
@@ -16288,10 +16330,10 @@
         <v>295</v>
       </c>
       <c r="E8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G8" t="s">
         <v>491</v>
@@ -16315,7 +16357,7 @@
         <v>10104</v>
       </c>
       <c r="N8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O8"/>
       <c r="P8"/>
@@ -16344,10 +16386,10 @@
         <v>298</v>
       </c>
       <c r="E9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G9" t="s">
         <v>502</v>
@@ -16371,7 +16413,7 @@
         <v>10104</v>
       </c>
       <c r="N9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O9"/>
       <c r="P9"/>
@@ -16400,10 +16442,10 @@
         <v>301</v>
       </c>
       <c r="E10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G10" t="s">
         <v>502</v>
@@ -16427,7 +16469,7 @@
         <v>10102</v>
       </c>
       <c r="N10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O10"/>
       <c r="P10"/>
@@ -16456,10 +16498,10 @@
         <v>304</v>
       </c>
       <c r="E11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G11" t="s">
         <v>502</v>
@@ -16483,7 +16525,7 @@
         <v>10176</v>
       </c>
       <c r="N11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O11"/>
       <c r="P11"/>
@@ -16512,10 +16554,10 @@
         <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G12" t="s">
         <v>502</v>
@@ -16539,7 +16581,7 @@
         <v>10176</v>
       </c>
       <c r="N12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O12"/>
       <c r="P12"/>
@@ -16568,10 +16610,10 @@
         <v>310</v>
       </c>
       <c r="E13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G13" t="s">
         <v>502</v>
@@ -16595,7 +16637,7 @@
         <v>21001</v>
       </c>
       <c r="N13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O13"/>
       <c r="P13"/>
@@ -16624,10 +16666,10 @@
         <v>519</v>
       </c>
       <c r="E14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G14" t="s">
         <v>520</v>
@@ -16651,7 +16693,7 @@
         <v>10104</v>
       </c>
       <c r="N14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O14"/>
       <c r="P14"/>
@@ -16680,10 +16722,10 @@
         <v>317</v>
       </c>
       <c r="E15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G15" t="s">
         <v>491</v>
@@ -16707,7 +16749,7 @@
         <v>21001</v>
       </c>
       <c r="N15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O15"/>
       <c r="P15"/>
@@ -16736,10 +16778,10 @@
         <v>319</v>
       </c>
       <c r="E16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G16" t="s">
         <v>520</v>
@@ -16763,7 +16805,7 @@
         <v>10102</v>
       </c>
       <c r="N16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O16"/>
       <c r="P16"/>
@@ -16792,10 +16834,10 @@
         <v>304</v>
       </c>
       <c r="E17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G17" t="s">
         <v>502</v>
@@ -16819,7 +16861,7 @@
         <v>10104</v>
       </c>
       <c r="N17" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O17"/>
       <c r="P17"/>
@@ -16848,10 +16890,10 @@
         <v>323</v>
       </c>
       <c r="E18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G18" t="s">
         <v>482</v>
@@ -16875,7 +16917,7 @@
         <v>10176</v>
       </c>
       <c r="N18" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O18"/>
       <c r="P18"/>
@@ -16904,10 +16946,10 @@
         <v>326</v>
       </c>
       <c r="E19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G19" t="s">
         <v>502</v>
@@ -16931,7 +16973,7 @@
         <v>21001</v>
       </c>
       <c r="N19" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O19"/>
       <c r="P19"/>
@@ -16960,10 +17002,10 @@
         <v>328</v>
       </c>
       <c r="E20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G20" t="s">
         <v>534</v>
@@ -16987,7 +17029,7 @@
         <v>10102</v>
       </c>
       <c r="N20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O20"/>
       <c r="P20"/>
@@ -17016,10 +17058,10 @@
         <v>333</v>
       </c>
       <c r="E21" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G21" t="s">
         <v>491</v>
@@ -17043,7 +17085,7 @@
         <v>10102</v>
       </c>
       <c r="N21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O21"/>
       <c r="P21"/>
@@ -17072,10 +17114,10 @@
         <v>336</v>
       </c>
       <c r="E22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G22" t="s">
         <v>502</v>
@@ -17099,7 +17141,7 @@
         <v>21001</v>
       </c>
       <c r="N22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O22"/>
       <c r="P22"/>
@@ -17128,10 +17170,10 @@
         <v>339</v>
       </c>
       <c r="E23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G23" t="s">
         <v>491</v>
@@ -17155,7 +17197,7 @@
         <v>10101</v>
       </c>
       <c r="N23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O23"/>
       <c r="P23"/>
@@ -17184,10 +17226,10 @@
         <v>342</v>
       </c>
       <c r="E24" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G24" t="s">
         <v>491</v>
@@ -17211,7 +17253,7 @@
         <v>10104</v>
       </c>
       <c r="N24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O24"/>
       <c r="P24"/>
@@ -17240,10 +17282,10 @@
         <v>345</v>
       </c>
       <c r="E25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G25" t="s">
         <v>491</v>
@@ -17267,7 +17309,7 @@
         <v>10104</v>
       </c>
       <c r="N25" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O25"/>
       <c r="P25"/>
@@ -17296,10 +17338,10 @@
         <v>351</v>
       </c>
       <c r="E26" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F26" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G26" t="s">
         <v>502</v>
@@ -17323,7 +17365,7 @@
         <v>10104</v>
       </c>
       <c r="N26" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O26"/>
       <c r="P26"/>
@@ -17352,10 +17394,10 @@
         <v>351</v>
       </c>
       <c r="E27" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F27" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G27" t="s">
         <v>482</v>
@@ -17379,7 +17421,7 @@
         <v>10107</v>
       </c>
       <c r="N27" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O27"/>
       <c r="P27"/>
@@ -17408,10 +17450,10 @@
         <v>554</v>
       </c>
       <c r="E28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G28" t="s">
         <v>520</v>
@@ -17435,7 +17477,7 @@
         <v>10104</v>
       </c>
       <c r="N28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O28"/>
       <c r="P28"/>
@@ -17464,10 +17506,10 @@
         <v>357</v>
       </c>
       <c r="E29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G29" t="s">
         <v>482</v>
@@ -17491,7 +17533,7 @@
         <v>21001</v>
       </c>
       <c r="N29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O29"/>
       <c r="P29"/>
@@ -17520,10 +17562,10 @@
         <v>361</v>
       </c>
       <c r="E30" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F30" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G30" t="s">
         <v>491</v>
@@ -17547,7 +17589,7 @@
         <v>10104</v>
       </c>
       <c r="N30" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O30"/>
       <c r="P30"/>
@@ -17576,13 +17618,13 @@
         <v>326</v>
       </c>
       <c r="E31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G31" t="s">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="H31" t="n" s="5">
         <v>46000</v>
@@ -17603,7 +17645,7 @@
         <v>21002</v>
       </c>
       <c r="N31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O31"/>
       <c r="P31"/>
@@ -17625,7 +17667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD02627-0AF2-4D0D-918E-F5CC976075FC}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
@@ -18379,6 +18421,68 @@
         <v>46259</v>
       </c>
     </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B13" t="s">
+        <v>560</v>
+      </c>
+      <c r="C13" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" t="s">
+        <v>573</v>
+      </c>
+      <c r="E13" t="s">
+        <v>484</v>
+      </c>
+      <c r="F13" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="G13" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="H13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="K13" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="L13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n" s="3">
+        <v>120000</v>
+      </c>
+      <c r="O13" t="n" s="3">
+        <v>120000</v>
+      </c>
+      <c r="P13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n" s="5">
+        <v>46356</v>
+      </c>
+      <c r="S13" t="n" s="5">
+        <v>46368</v>
+      </c>
+      <c r="T13" t="n" s="5">
+        <v>46733</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18386,7 +18490,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1EB3EA1-AA35-477F-A30B-FD77D094C1DA}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="25.6640625" customWidth="1"/>
@@ -18448,7 +18552,7 @@
         <v>481</v>
       </c>
       <c r="F2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G2" t="n" s="3">
         <v>429382.89</v>
@@ -18476,13 +18580,13 @@
         <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E3" t="s">
         <v>481</v>
       </c>
       <c r="F3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G3" t="n" s="3">
         <v>429382.89</v>
@@ -18518,7 +18622,7 @@
         <v>486</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G4" t="n" s="3">
         <v>122825171.15</v>
@@ -18546,13 +18650,13 @@
         <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E5" t="s">
         <v>486</v>
       </c>
       <c r="F5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G5" t="n" s="3">
         <v>122825171.15</v>
@@ -18588,7 +18692,7 @@
         <v>490</v>
       </c>
       <c r="F6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G6" t="n" s="3">
         <v>20493161.89</v>
@@ -18620,7 +18724,7 @@
         <v>495</v>
       </c>
       <c r="F7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G7" t="n" s="3">
         <v>633847.5</v>
@@ -18652,7 +18756,7 @@
         <v>498</v>
       </c>
       <c r="F8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G8" t="n" s="3">
         <v>225677</v>
@@ -18684,7 +18788,7 @@
         <v>501</v>
       </c>
       <c r="F9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G9" t="n" s="3">
         <v>96000</v>
@@ -18716,7 +18820,7 @@
         <v>504</v>
       </c>
       <c r="F10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G10" t="n" s="3">
         <v>72000</v>
@@ -18748,7 +18852,7 @@
         <v>506</v>
       </c>
       <c r="F11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G11" t="n" s="3">
         <v>60000</v>
@@ -18780,7 +18884,7 @@
         <v>509</v>
       </c>
       <c r="F12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G12" t="n" s="3">
         <v>60000</v>
@@ -18812,7 +18916,7 @@
         <v>511</v>
       </c>
       <c r="F13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G13" t="n" s="3">
         <v>42000</v>
@@ -18844,7 +18948,7 @@
         <v>513</v>
       </c>
       <c r="F14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G14" t="n" s="3">
         <v>72000</v>
@@ -18876,7 +18980,7 @@
         <v>515</v>
       </c>
       <c r="F15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G15" t="n" s="3">
         <v>60000</v>
@@ -18908,7 +19012,7 @@
         <v>518</v>
       </c>
       <c r="F16" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G16" t="n" s="3">
         <v>60000</v>
@@ -18936,13 +19040,13 @@
         <v>232</v>
       </c>
       <c r="D17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E17" t="s">
         <v>518</v>
       </c>
       <c r="F17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G17" t="n" s="3">
         <v>60000</v>
@@ -18974,13 +19078,13 @@
         <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E18" t="s">
         <v>518</v>
       </c>
       <c r="F18" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G18" t="n" s="3">
         <v>60000</v>
@@ -19012,13 +19116,13 @@
         <v>232</v>
       </c>
       <c r="D19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E19" t="s">
         <v>518</v>
       </c>
       <c r="F19" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G19" t="n" s="3">
         <v>540000</v>
@@ -19054,7 +19158,7 @@
         <v>523</v>
       </c>
       <c r="F20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G20" t="n" s="3">
         <v>60000</v>
@@ -19086,7 +19190,7 @@
         <v>525</v>
       </c>
       <c r="F21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G21" t="n" s="3">
         <v>60000</v>
@@ -19114,13 +19218,13 @@
         <v>232</v>
       </c>
       <c r="D22" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E22" t="s">
         <v>525</v>
       </c>
       <c r="F22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G22" t="n" s="3">
         <v>60000</v>
@@ -19152,13 +19256,13 @@
         <v>232</v>
       </c>
       <c r="D23" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E23" t="s">
         <v>525</v>
       </c>
       <c r="F23" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G23" t="n" s="3">
         <v>540000</v>
@@ -19194,7 +19298,7 @@
         <v>527</v>
       </c>
       <c r="F24" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G24" t="n" s="3">
         <v>96000</v>
@@ -19226,7 +19330,7 @@
         <v>529</v>
       </c>
       <c r="F25" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G25" t="n" s="3">
         <v>187475</v>
@@ -19254,13 +19358,13 @@
         <v>232</v>
       </c>
       <c r="D26" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E26" t="s">
         <v>529</v>
       </c>
       <c r="F26" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G26" t="n" s="3">
         <v>187475</v>
@@ -19296,7 +19400,7 @@
         <v>531</v>
       </c>
       <c r="F27" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G27" t="n" s="3">
         <v>60000</v>
@@ -19328,7 +19432,7 @@
         <v>533</v>
       </c>
       <c r="F28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G28" t="n" s="3">
         <v>36000</v>
@@ -19360,7 +19464,7 @@
         <v>333</v>
       </c>
       <c r="F29" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G29" t="n" s="3">
         <v>72000</v>
@@ -19392,7 +19496,7 @@
         <v>537</v>
       </c>
       <c r="F30" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G30" t="n" s="3">
         <v>92400</v>
@@ -19424,7 +19528,7 @@
         <v>540</v>
       </c>
       <c r="F31" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G31" t="n" s="3">
         <v>44400</v>
@@ -19456,7 +19560,7 @@
         <v>543</v>
       </c>
       <c r="F32" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G32" t="n" s="3">
         <v>66000</v>
@@ -19488,7 +19592,7 @@
         <v>546</v>
       </c>
       <c r="F33" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G33" t="n" s="3">
         <v>63360</v>
@@ -19520,7 +19624,7 @@
         <v>549</v>
       </c>
       <c r="F34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G34" t="n" s="3">
         <v>48000</v>
@@ -19552,7 +19656,7 @@
         <v>551</v>
       </c>
       <c r="F35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G35" t="n" s="3">
         <v>48000</v>
@@ -19580,13 +19684,13 @@
         <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E36" t="s">
         <v>551</v>
       </c>
       <c r="F36" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G36" t="n" s="3">
         <v>48000</v>
@@ -19622,7 +19726,7 @@
         <v>553</v>
       </c>
       <c r="F37" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G37" t="n" s="3">
         <v>30000</v>
@@ -19650,13 +19754,13 @@
         <v>232</v>
       </c>
       <c r="D38" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E38" t="s">
         <v>553</v>
       </c>
       <c r="F38" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G38" t="n" s="3">
         <v>30000</v>
@@ -19692,7 +19796,7 @@
         <v>556</v>
       </c>
       <c r="F39" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G39" t="n" s="3">
         <v>229329.84</v>
@@ -19720,13 +19824,13 @@
         <v>232</v>
       </c>
       <c r="D40" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E40" t="s">
         <v>556</v>
       </c>
       <c r="F40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G40" t="n" s="3">
         <v>229329.84</v>
@@ -19762,7 +19866,7 @@
         <v>361</v>
       </c>
       <c r="F41" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G41" t="n" s="3">
         <v>60000</v>
@@ -19794,7 +19898,7 @@
         <v>326</v>
       </c>
       <c r="F42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G42" t="n" s="3">
         <v>60000</v>
@@ -19809,6 +19913,44 @@
       </c>
       <c r="L42" t="n" s="3">
         <v>60000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>362</v>
+      </c>
+      <c r="C43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D43" t="s">
+        <v>585</v>
+      </c>
+      <c r="E43" t="s">
+        <v>326</v>
+      </c>
+      <c r="F43" t="s">
+        <v>431</v>
+      </c>
+      <c r="G43" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="H43" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="I43" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="J43" t="n" s="3">
+        <v>60000</v>
+      </c>
+      <c r="K43" t="n" s="3">
+        <v>120000</v>
+      </c>
+      <c r="L43" t="n" s="3">
+        <v>120000</v>
       </c>
     </row>
   </sheetData>
@@ -19878,7 +20020,7 @@
         <v>486</v>
       </c>
       <c r="F2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G2" t="n" s="3">
         <v>122825171.15</v>
@@ -19888,10 +20030,10 @@
         <v>122825171.15</v>
       </c>
       <c r="J2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -19964,10 +20106,10 @@
         <v>481</v>
       </c>
       <c r="F2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2" t="n" s="3">
         <v>4293.83</v>
@@ -19982,7 +20124,7 @@
         <v>4293.83</v>
       </c>
       <c r="L2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -20000,10 +20142,10 @@
         <v>481</v>
       </c>
       <c r="F3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H3" t="n" s="3">
         <v>42938.29</v>
@@ -20018,7 +20160,7 @@
         <v>42938.29</v>
       </c>
       <c r="L3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -20032,16 +20174,16 @@
         <v>480</v>
       </c>
       <c r="D4" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E4" t="s">
         <v>481</v>
       </c>
       <c r="F4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H4" t="n" s="3">
         <v>58044.68</v>
@@ -20056,7 +20198,7 @@
         <v>73151.07</v>
       </c>
       <c r="L4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -20070,16 +20212,16 @@
         <v>480</v>
       </c>
       <c r="D5" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E5" t="s">
         <v>481</v>
       </c>
       <c r="F5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H5" t="n" s="3">
         <v>58044.68</v>
@@ -20094,7 +20236,7 @@
         <v>100982.97</v>
       </c>
       <c r="L5" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -20112,10 +20254,10 @@
         <v>486</v>
       </c>
       <c r="F6" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H6" t="n" s="3">
         <v>24565034.23</v>
@@ -20130,7 +20272,7 @@
         <v>24565034.23</v>
       </c>
       <c r="L6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -20144,16 +20286,16 @@
         <v>485</v>
       </c>
       <c r="D7" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E7" t="s">
         <v>486</v>
       </c>
       <c r="F7" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="G7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H7" t="n" s="3">
         <v>24565034.23</v>
@@ -20168,7 +20310,7 @@
         <v>49130068.46</v>
       </c>
       <c r="L7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -20186,10 +20328,10 @@
         <v>490</v>
       </c>
       <c r="F8" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H8" t="n" s="3">
         <v>2049316</v>
@@ -20204,7 +20346,7 @@
         <v>2049316</v>
       </c>
       <c r="L8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -20218,16 +20360,16 @@
         <v>489</v>
       </c>
       <c r="D9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E9" t="s">
         <v>490</v>
       </c>
       <c r="F9" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H9" t="n" s="3">
         <v>2049316</v>
@@ -20242,7 +20384,7 @@
         <v>4098632</v>
       </c>
       <c r="L9" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -20288,10 +20430,10 @@
         <v>45566</v>
       </c>
       <c r="D2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -20305,10 +20447,10 @@
         <v>45750</v>
       </c>
       <c r="D3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -20322,10 +20464,10 @@
         <v>45750</v>
       </c>
       <c r="D4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E4" t="s">
         <v>599</v>
-      </c>
-      <c r="E4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -20339,10 +20481,10 @@
         <v>45750</v>
       </c>
       <c r="D5" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
